--- a/EPIB704_HW_data_2026/CARDS_data_dictionary.xlsx
+++ b/EPIB704_HW_data_2026/CARDS_data_dictionary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://mcgill-my.sharepoint.com/personal/mabel_carabali_mcgill_ca/Documents/EPIB_704/EPIB704_Course_Info_General/EPIB704_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A2C11BE4-CB5E-8140-A869-136F98C28117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="8_{A2C11BE4-CB5E-8140-A869-136F98C28117}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0F877F21-9E5A-324D-BE23-A8C711FC4872}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1000" windowWidth="27640" windowHeight="16060" xr2:uid="{CAF37AEA-D32F-6643-BC11-B6AB3C972F51}"/>
+    <workbookView xWindow="780" yWindow="960" windowWidth="27640" windowHeight="16060" xr2:uid="{CAF37AEA-D32F-6643-BC11-B6AB3C972F51}"/>
   </bookViews>
   <sheets>
     <sheet name="Variable dictionary" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="106">
   <si>
     <t>Variable</t>
   </si>
@@ -345,6 +345,18 @@
   </si>
   <si>
     <t xml:space="preserve">Non available information </t>
+  </si>
+  <si>
+    <t>Comorbidities</t>
+  </si>
+  <si>
+    <t>Number of Cardiometabolic Comorbidies among any of Obesity, Hypertension and Diabetes</t>
+  </si>
+  <si>
+    <t>comorb.bin</t>
+  </si>
+  <si>
+    <t>Presence of any cardiometabolic comorbidities</t>
   </si>
 </sst>
 </file>
@@ -695,7 +707,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D5B57F51-785B-B04C-979F-1420EE1651C4}">
-  <dimension ref="A1:B51"/>
+  <dimension ref="A1:B53"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="43.6640625" customWidth="1"/>
@@ -1110,6 +1122,22 @@
         <v>101</v>
       </c>
     </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A52" t="s">
+        <v>102</v>
+      </c>
+      <c r="B52" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.2">
+      <c r="A53" t="s">
+        <v>104</v>
+      </c>
+      <c r="B53" t="s">
+        <v>105</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
